--- a/data/cashflows.xlsx
+++ b/data/cashflows.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="13">
   <si>
     <t>loan_id</t>
   </si>
@@ -28,7 +28,13 @@
     <t>interest_pik</t>
   </si>
   <si>
-    <t>principal</t>
+    <t>principal_repayment</t>
+  </si>
+  <si>
+    <t>prepayment</t>
+  </si>
+  <si>
+    <t>principal_draw</t>
   </si>
   <si>
     <t>fees</t>
@@ -48,41 +54,14 @@
   <si>
     <t>L005</t>
   </si>
-  <si>
-    <t>2024-10-15</t>
-  </si>
-  <si>
-    <t>2024-11-15</t>
-  </si>
-  <si>
-    <t>2024-12-15</t>
-  </si>
-  <si>
-    <t>2024-10-20</t>
-  </si>
-  <si>
-    <t>2024-11-20</t>
-  </si>
-  <si>
-    <t>2024-10-10</t>
-  </si>
-  <si>
-    <t>2024-12-10</t>
-  </si>
-  <si>
-    <t>2024-11-30</t>
-  </si>
-  <si>
-    <t>2024-10-05</t>
-  </si>
-  <si>
-    <t>2024-12-05</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -135,11 +114,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -434,10 +414,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -456,16 +436,22 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="B2" s="2">
+        <v>45322</v>
       </c>
       <c r="C2">
-        <v>520000</v>
+        <v>141666.6666666666</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -474,18 +460,24 @@
         <v>0</v>
       </c>
       <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>2000000</v>
+      </c>
+      <c r="H2">
         <v>15000</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
+        <v>8</v>
+      </c>
+      <c r="B3" s="2">
+        <v>45351</v>
       </c>
       <c r="C3">
-        <v>525000</v>
+        <v>162916.6666666666</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -496,16 +488,22 @@
       <c r="F3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3">
+        <v>3000000</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
+        <v>8</v>
+      </c>
+      <c r="B4" s="2">
+        <v>45382</v>
       </c>
       <c r="C4">
-        <v>530000</v>
+        <v>162916.6666666666</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -516,39 +514,51 @@
       <c r="F4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
+        <v>8</v>
+      </c>
+      <c r="B5" s="2">
+        <v>45412</v>
       </c>
       <c r="C5">
-        <v>380000</v>
+        <v>170000</v>
       </c>
       <c r="D5">
-        <v>60000</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>1000000</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
+        <v>8</v>
+      </c>
+      <c r="B6" s="2">
+        <v>45443</v>
       </c>
       <c r="C6">
-        <v>360000</v>
+        <v>177083.3333333333</v>
       </c>
       <c r="D6">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -556,104 +566,1440 @@
       <c r="F6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="G6">
+        <v>1000000</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" t="s">
-        <v>16</v>
+      <c r="B7" s="2">
+        <v>45473</v>
       </c>
       <c r="C7">
-        <v>700000</v>
+        <v>177083.3333333333</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" t="s">
-        <v>17</v>
+      <c r="B8" s="2">
+        <v>45504</v>
       </c>
       <c r="C8">
-        <v>690000</v>
+        <v>175666.6666666667</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
+        <v>200000</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <v>45535</v>
+      </c>
+      <c r="C9">
+        <v>174250</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>200000</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
+        <v>45565</v>
+      </c>
+      <c r="C10">
+        <v>172833.3333333333</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>200000</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2">
+        <v>45596</v>
+      </c>
+      <c r="C11">
+        <v>164333.3333333333</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>200000</v>
+      </c>
+      <c r="F11">
+        <v>1000000</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="2">
+        <v>45626</v>
+      </c>
+      <c r="C12">
+        <v>162916.6666666666</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>200000</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="2">
+        <v>45657</v>
+      </c>
+      <c r="C13">
+        <v>161500</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>200000</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="2">
+        <v>45322</v>
+      </c>
+      <c r="C14">
+        <v>100208.3333333333</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>3000000</v>
+      </c>
+      <c r="H14">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="2">
+        <v>45351</v>
+      </c>
+      <c r="C15">
+        <v>100208.3333333333</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="2">
+        <v>45382</v>
+      </c>
+      <c r="C16">
+        <v>123333.3333333333</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>3000000</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="2">
+        <v>45412</v>
+      </c>
+      <c r="C17">
+        <v>123333.3333333333</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="2">
+        <v>45443</v>
+      </c>
+      <c r="C18">
+        <v>138750</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>2000000</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="2">
+        <v>45473</v>
+      </c>
+      <c r="C19">
+        <v>79212.5</v>
+      </c>
+      <c r="D19">
+        <v>60000</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="2">
+        <v>45504</v>
+      </c>
+      <c r="C20">
+        <v>79675</v>
+      </c>
+      <c r="D20">
+        <v>60000</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="2">
+        <v>45535</v>
+      </c>
+      <c r="C21">
+        <v>78981.25</v>
+      </c>
+      <c r="D21">
+        <v>60000</v>
+      </c>
+      <c r="E21">
+        <v>150000</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="2">
+        <v>45565</v>
+      </c>
+      <c r="C22">
+        <v>137825</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>150000</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="2">
+        <v>45596</v>
+      </c>
+      <c r="C23">
+        <v>136668.75</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>150000</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="2">
+        <v>45626</v>
+      </c>
+      <c r="C24">
+        <v>135512.5</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>150000</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="2">
+        <v>45657</v>
+      </c>
+      <c r="C25">
+        <v>130502.0833333333</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>150000</v>
+      </c>
+      <c r="F25">
         <v>500000</v>
       </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9">
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>10</v>
+      </c>
+      <c r="B26" s="2">
+        <v>45322</v>
+      </c>
+      <c r="C26">
+        <v>249375</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>500000</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" t="s">
+        <v>10</v>
+      </c>
+      <c r="B27" s="2">
+        <v>45351</v>
+      </c>
+      <c r="C27">
+        <v>245416.6666666667</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>500000</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" t="s">
+        <v>10</v>
+      </c>
+      <c r="B28" s="2">
+        <v>45382</v>
+      </c>
+      <c r="C28">
+        <v>241458.3333333333</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>500000</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29" s="2">
+        <v>45412</v>
+      </c>
+      <c r="C29">
+        <v>237500</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>500000</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" t="s">
+        <v>10</v>
+      </c>
+      <c r="B30" s="2">
+        <v>45443</v>
+      </c>
+      <c r="C30">
+        <v>233541.6666666667</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>500000</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" t="s">
+        <v>10</v>
+      </c>
+      <c r="B31" s="2">
+        <v>45473</v>
+      </c>
+      <c r="C31">
+        <v>229583.3333333333</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>500000</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32" s="2">
+        <v>45504</v>
+      </c>
+      <c r="C32">
+        <v>225625</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>500000</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33" s="2">
+        <v>45535</v>
+      </c>
+      <c r="C33">
+        <v>221666.6666666667</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>500000</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" s="2">
+        <v>45565</v>
+      </c>
+      <c r="C34">
+        <v>205833.3333333333</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>500000</v>
+      </c>
+      <c r="F34">
+        <v>1500000</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" t="s">
+        <v>10</v>
+      </c>
+      <c r="B35" s="2">
+        <v>45596</v>
+      </c>
+      <c r="C35">
+        <v>201875</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>500000</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" t="s">
+        <v>10</v>
+      </c>
+      <c r="B36" s="2">
+        <v>45626</v>
+      </c>
+      <c r="C36">
+        <v>197916.6666666667</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>500000</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" t="s">
+        <v>10</v>
+      </c>
+      <c r="B37" s="2">
+        <v>45657</v>
+      </c>
+      <c r="C37">
+        <v>193958.3333333333</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>500000</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="C38">
+        <v>70000</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" s="2">
+        <v>45351</v>
+      </c>
+      <c r="C39">
+        <v>87500</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>2000000</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40" s="2">
+        <v>45382</v>
+      </c>
+      <c r="C40">
+        <v>105000</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>2000000</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41" s="2">
+        <v>45412</v>
+      </c>
+      <c r="C41">
+        <v>105000</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" t="s">
+        <v>11</v>
+      </c>
+      <c r="B42" s="2">
+        <v>45443</v>
+      </c>
+      <c r="C42">
+        <v>105000</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" t="s">
+        <v>11</v>
+      </c>
+      <c r="B43" s="2">
+        <v>45473</v>
+      </c>
+      <c r="C43">
+        <v>113750</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>1000000</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44" s="2">
+        <v>45504</v>
+      </c>
+      <c r="C44">
+        <v>113750</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" t="s">
+        <v>11</v>
+      </c>
+      <c r="B45" s="2">
+        <v>45535</v>
+      </c>
+      <c r="C45">
+        <v>113750</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" s="2">
+        <v>45565</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>120000</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" t="s">
+        <v>11</v>
+      </c>
+      <c r="B47" s="2">
+        <v>45596</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>120000</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" t="s">
+        <v>11</v>
+      </c>
+      <c r="B48" s="2">
+        <v>45626</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>120000</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" t="s">
+        <v>11</v>
+      </c>
+      <c r="B49" s="2">
+        <v>45657</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>120000</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" t="s">
+        <v>12</v>
+      </c>
+      <c r="B50" s="2">
+        <v>45322</v>
+      </c>
+      <c r="C50">
+        <v>163125</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
         <v>250000</v>
       </c>
-      <c r="D9">
-        <v>120000</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10">
-        <v>410000</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11">
-        <v>415000</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" s="2">
+        <v>45351</v>
+      </c>
+      <c r="C51">
+        <v>161250</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>250000</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52" s="2">
+        <v>45382</v>
+      </c>
+      <c r="C52">
+        <v>159375</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+      <c r="E52">
+        <v>250000</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" t="s">
+        <v>12</v>
+      </c>
+      <c r="B53" s="2">
+        <v>45412</v>
+      </c>
+      <c r="C53">
+        <v>157500</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <v>250000</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" t="s">
+        <v>12</v>
+      </c>
+      <c r="B54" s="2">
+        <v>45443</v>
+      </c>
+      <c r="C54">
+        <v>155625</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>250000</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" t="s">
+        <v>12</v>
+      </c>
+      <c r="B55" s="2">
+        <v>45473</v>
+      </c>
+      <c r="C55">
+        <v>153750</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>250000</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" t="s">
+        <v>12</v>
+      </c>
+      <c r="B56" s="2">
+        <v>45504</v>
+      </c>
+      <c r="C56">
+        <v>145875</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56">
+        <v>250000</v>
+      </c>
+      <c r="F56">
+        <v>800000</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" t="s">
+        <v>12</v>
+      </c>
+      <c r="B57" s="2">
+        <v>45535</v>
+      </c>
+      <c r="C57">
+        <v>144000</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57">
+        <v>250000</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" t="s">
+        <v>12</v>
+      </c>
+      <c r="B58" s="2">
+        <v>45565</v>
+      </c>
+      <c r="C58">
+        <v>142125</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="E58">
+        <v>250000</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" t="s">
+        <v>12</v>
+      </c>
+      <c r="B59" s="2">
+        <v>45596</v>
+      </c>
+      <c r="C59">
+        <v>140250</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <v>250000</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" t="s">
+        <v>12</v>
+      </c>
+      <c r="B60" s="2">
+        <v>45626</v>
+      </c>
+      <c r="C60">
+        <v>138375</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>250000</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" t="s">
+        <v>12</v>
+      </c>
+      <c r="B61" s="2">
+        <v>45657</v>
+      </c>
+      <c r="C61">
+        <v>136500</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <v>250000</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
         <v>0</v>
       </c>
     </row>
